--- a/java/spring/xlsx表格文件/spring-jdbc 5.2.9 包所有的类.xlsx
+++ b/java/spring/xlsx表格文件/spring-jdbc 5.2.9 包所有的类.xlsx
@@ -957,7 +957,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -967,13 +967,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1542,51 +1535,54 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1596,101 +1592,98 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1728,7 +1721,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2395,7 +2387,7 @@
     <col min="3" max="3" width="54.6666666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="79.2" spans="1:3">
+    <row r="1" ht="66" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>217</v>
       </c>
@@ -2442,7 +2434,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" ht="26.4" spans="1:3">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>226</v>
       </c>
@@ -2490,7 +2482,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="14" ht="52.8" spans="1:3">
+    <row r="14" ht="39.6" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -2514,7 +2506,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" ht="52.8" spans="1:3">
+    <row r="17" ht="39.6" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>240</v>
       </c>
@@ -2552,7 +2544,7 @@
     <col min="3" max="3" width="67" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="66" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>244</v>
       </c>
@@ -2921,7 +2913,7 @@
       <c r="B2" s="9"/>
       <c r="C2" s="10"/>
     </row>
-    <row r="3" ht="26.4" spans="1:3">
+    <row r="3" spans="1:3">
       <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
@@ -3086,7 +3078,7 @@
       </c>
       <c r="C20" s="10"/>
     </row>
-    <row r="21" ht="52.8" spans="1:5">
+    <row r="21" ht="26.4" spans="1:5">
       <c r="A21" s="9"/>
       <c r="B21" s="8" t="s">
         <v>41</v>
@@ -3129,8 +3121,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" ht="66" spans="1:3">
-      <c r="A25" s="19" t="s">
+    <row r="25" ht="26.4" spans="1:3">
+      <c r="A25" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -3140,7 +3132,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="39.6" spans="1:3">
+    <row r="26" ht="26.4" spans="1:3">
       <c r="A26" s="11" t="s">
         <v>51</v>
       </c>
@@ -3192,7 +3184,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" ht="39.6" spans="1:3">
+    <row r="32" spans="1:3">
       <c r="A32" s="8" t="s">
         <v>59</v>
       </c>
@@ -3223,8 +3215,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" ht="91.2" spans="1:3">
-      <c r="A35" s="20" t="s">
+    <row r="35" ht="39.6" spans="1:3">
+      <c r="A35" s="19" t="s">
         <v>65</v>
       </c>
       <c r="B35" s="9"/>
@@ -3246,7 +3238,7 @@
       <c r="B37" s="9"/>
       <c r="C37" s="10"/>
     </row>
-    <row r="38" ht="66" spans="1:3">
+    <row r="38" ht="26.4" spans="1:3">
       <c r="A38" s="8" t="s">
         <v>69</v>
       </c>
